--- a/files/Archive/Spinney_Budget_Tracker_v4.xlsx
+++ b/files/Archive/Spinney_Budget_Tracker_v4.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="347">
   <si>
     <t xml:space="preserve">Spinney External Works — Budget Summary</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">LG Building and Roofing Ltd</t>
   </si>
   <si>
-    <t xml:space="preserve">Labour £17,600 (no VAT), not yet started. EXCLUDED from 10% discount. Rubbish removal (£1,200) transferred 10 Aug to pooled skip fund — see that row, not double-counted here.</t>
+    <t xml:space="preserve">Labour £17,600 (no VAT). Stage 1 (£4,400) invoiced/paid 20 Aug, full price. Cash instalment (£2,000, 4 Sep) — CORRECTED: cash payments DO get the 10% discount (same as chimney/coping), retiring £2,222.22 of quoted value. £6,400 cash paid to date, equivalent to £6,622.22 of quoted value — £10,977.78 quoted value remaining. Rubbish removal (£1,200) transferred 10 Aug to pooled skip fund — see that row, not double-counted here.</t>
   </si>
   <si>
     <t xml:space="preserve">Contingency</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Snapshot</t>
   </si>
   <si>
-    <t xml:space="preserve">Week 5 — overall, we are running close to plan. The three areas with a real written quote (chimney, coping, decking) are on or under budget; the only genuine overrun is £62.90 on pooled materials. Contingency is barely touched. Nothing here suggests a budget problem yet.</t>
+    <t xml:space="preserve">Week 5 — overall, we are running close to plan. Chimney, coping, and decking materials all landed on or under quote; decking labour's first stage matches the quoted rate exactly. Materials pool is back under its cap after a refund. Contingency is barely touched. Nothing here suggests a budget problem.</t>
   </si>
   <si>
     <t xml:space="preserve">• Chimney</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">• Decking (labour + V4 materials)</t>
   </si>
   <si>
-    <t xml:space="preserve">£0 variance so far — materials fully paid to the V4 proforma exactly; labour not yet started, still sitting at the quoted £17,600.</t>
+    <t xml:space="preserve">Materials fully paid to the V4 proforma exactly. Labour: Stage 1 (£4,400) invoiced full price, plus a £2,000 cash instalment (4 Sep, 10% discount applies) — £6,400 paid so far, £11,200 quoted value remaining across future stages.</t>
   </si>
   <si>
     <t xml:space="preserve">• Scaffold (pooled, chimney + coping combined)</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">• Materials (pooled, chimney + coping)</t>
   </si>
   <si>
-    <t xml:space="preserve">£62.90 OVER the £1,130 cap — driven by pooling Luke's own Travis Perkins account purchases (across 4 invoices, render/masonry consumables) into the fund alongside Dry Lining Supplies, same simplified treatment throughout, not split by workstream. Cap left at £1,130 deliberately (flagged, not raised). Worth checking with Luke whether any unused stock can go back to store for a refund.</t>
+    <t xml:space="preserve">Back under the £1,130 cap — a £72.23 refund from Dry Lining Supplies (unused monocouche + other returned items) landed 19 Aug, more than offsetting the earlier £62.90 overage from pooling Luke's Travis Perkins account purchases.</t>
   </si>
   <si>
     <t xml:space="preserve">• Rubbish removal (pooled, all 3 workstreams)</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">• Contingency</t>
   </si>
   <si>
-    <t xml:space="preserve">£339.32 drawn of the £5,000 pot (condensation-prep £276.42 + chimney cowl upgrade £62.90) — £4,660.68 remaining. Both draws are genuine scope additions beyond the original quotes, which is exactly what this pot is for.</t>
+    <t xml:space="preserve">£480.98 drawn of the £5,000 pot (condensation-prep £276.42 + chimney cowl upgrade £62.90 + V4 screw top-up £141.66) — £4,519.02 remaining. All three are genuine scope additions beyond the original quotes, which is exactly what this pot is for.</t>
   </si>
   <si>
     <t xml:space="preserve">Budget vs Actual — detail</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Decking (labour)</t>
   </si>
   <si>
-    <t xml:space="preserve">Not yet started — committed, not incurred</t>
+    <t xml:space="preserve">Stage 1 (£4,400, invoiced, full price) + cash instalment (£2,000, 10% discount, retires £2,222.22 of quoted value) — £11,200 quoted value remaining, mix of future cash/invoice TBC.</t>
   </si>
   <si>
     <t xml:space="preserve">Decking materials (V4)</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">Materials (pooled, chimney+coping)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cap breached by pooling Luke's TP account purchases (4 invoices, all now paid in full 18 Aug, £547.88 total) — flagged, not raised.</t>
+    <t xml:space="preserve">Back under the £1,130 cap after a £72.23 refund from Dry Lining Supplies (unused monocouche + other returned items) landed 19 Aug — was £62.92 over before the refund.</t>
   </si>
   <si>
     <t xml:space="preserve">Rubbish removal (pooled, all 3 workstreams)</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">Decking's £1,200 share largely untested — see snapshot caveat</t>
   </si>
   <si>
-    <t xml:space="preserve">£339.32 drawn (condensation-prep £276.42 + chimney cowl £62.90) — £4,660.68 unused so far. Variance here just means 'not yet drawn', not a saving.</t>
+    <t xml:space="preserve">£480.98 drawn (condensation-prep £276.42 + chimney cowl £62.90 + V4 screw top-up £141.66) — £4,519.02 remaining. Variance here just means 'not yet drawn', not a saving.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL (as spent/committed to date)</t>
@@ -386,19 +386,16 @@
     <t xml:space="preserve">Terms confirmed 7 Aug: 100% cash (labour + materials) once priced. Separate from the base coping 50/50 split.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decking labour &amp; rubbish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4–5 stages — triggers TBC with Luke/Lara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">£17,600 labour total across stages. EXCLUDED from 10% labour discount. Rubbish removal transferred to pooled skip fund.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approved 20 Jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggested triggers: start / substructure (a) / Gate 2 / substructure (b) / Gate 3 — to be pinned</t>
+    <t xml:space="preserve">Stage 1 (25%, INV-0289) PAID 20 Aug — 4 stages confirmed, flat 25% each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£17,600 labour total across stages, at quoted rates. CORRECTED 4 Sep: cash payments DO get the 10% discount (same as chimney/coping) — only invoiced stages are full price. Rubbish removal transferred to pooled skip fund.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 1 paid, 25% down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 1 (£4,400) invoiced/paid 20 Aug, full price. Cash top-up (£2,000, 4 Sep) retires £2,222.22 of quoted value at the 10% discount. Remaining quoted value: £10,977.78. Exact milestone triggers for future stages still TBC.</t>
   </si>
   <si>
     <t xml:space="preserve">Periodic — on receipts</t>
@@ -548,7 +545,7 @@
     <t xml:space="preserve">Labour — remove old decking &amp; frame, construct composite frame, install deck to spec</t>
   </si>
   <si>
-    <t xml:space="preserve">RISK: pending structure/ground assessment. EXCLUDED from 10% labour discount (20 Jul).</t>
+    <t xml:space="preserve">RISK: pending structure/ground assessment. CORRECTED 4 Sep: cash payments DO get the 10% discount (same as chimney/coping) — only invoiced stages are full price. Progress: Stage 1 (£4,400) invoiced 20 Aug + £2,000 cash instalment 4 Sep (retires £2,222.22 of quoted value) — £6,400 cash paid to date, equivalent to £6,622.22 of quoted value — £10,977.78 quoted value remaining.</t>
   </si>
   <si>
     <t xml:space="preserve">Rubbish removal (8-yard skips ×2, possibly 3)</t>
@@ -596,6 +593,9 @@
     <t xml:space="preserve">Subframe hexhead screws — box of 50 (FH90P050)</t>
   </si>
   <si>
+    <t xml:space="preserve">Original 16 boxes delivered in full, confirmed 12 Aug. TOP-UP REQUESTED 20 Aug: Luke has asked for 15 more boxes (same item, FH90P050) — substructure screw consumption running ahead of the original estimate. Not yet ordered/invoiced. Estimated cost £141.66 inc VAT (15 x £7.87 + 20% VAT, matching original per-unit price) — treat as V4 Phase 3 once ordered. Not yet added to committed total.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Millboard touch-up paint — Ashwood (AP500H)</t>
   </si>
   <si>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">TBC</t>
   </si>
   <si>
-    <t xml:space="preserve">Contingency pot — fence labour, soakaway fix, garage drainage, curved-deck labour, cement &amp; bricks, coping condensation-prep (£250, reclassified 13 Aug)</t>
+    <t xml:space="preserve">Contingency pot — fence labour, garage drainage, curved-deck labour, cement &amp; bricks, coping condensation-prep (£250, reclassified 13 Aug). Soakaway fix cancelled 1 Sep, nothing drawn. Pipe investigation resolved 4 Sep — no leak, no repair needed, no draw required.</t>
   </si>
   <si>
     <t xml:space="preserve">As incurred</t>
@@ -659,10 +659,13 @@
     <t xml:space="preserve">RECLASSIFIED 17 Aug: lead flashing reattributed from chimney to coping (original quote explicitly scopes 'lead flashings to parapet rear' under coping's labour). Both items within originally-quoted scope, so routed through Materials pool per agreed rule rather than Coping's own Cost Lines.</t>
   </si>
   <si>
-    <t xml:space="preserve">Damplas DPC roll, 450mm x 30m (£26.42 inc VAT) — matches the condensation-prep spec (weep holes above damp-course membrane), named purpose #6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Settlement agreed 17 Aug. Added to the existing coping condensation-prep draw (purpose #6) — same work, this is the material for it. Total purpose #6 draw now £276.42 (£250 labour + £26.42 material).</t>
+    <t xml:space="preserve">Named purpose #8 — V4 screw top-up: 15 more boxes of Timberfix structural subframe screws (FH90P050), quote V4FQ-17702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requested by Luke 20 Aug, ordered 24 Aug, PAID. Substructure screw consumption ran ahead of the original 16-box estimate. Same item/supplier as the original V4 order, but treated as an additional-scope purchase per Ryan's direction — routed through Contingency rather than inflating the Decking materials (V4) line, which stays matched to its original proforma.</t>
   </si>
   <si>
     <t xml:space="preserve">Provisional pooled budget — transferred from chimney (£80) + coping (£80) + decking (£1,200) rubbish-removal quotes, 10 Aug. Family now supplies skips directly.</t>
@@ -746,9 +749,6 @@
     <t xml:space="preserve">Chimney labour, invoiced (£3,200 less £111.70 work-platform prepayment). Rubbish removal £80 NOT included — outstanding.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bank transfer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Invoiced (non-cash) — full price, no 10% discount. £80 rubbish removal still outstanding.</t>
   </si>
   <si>
@@ -872,6 +872,15 @@
     <t xml:space="preserve">PAID 18 Aug, confirmed as part of the full £547.88 TP account settlement (all 4 invoices). £0.02 rounding absorbed here so the three allocations reconcile exactly to the confirmed total.</t>
   </si>
   <si>
+    <t xml:space="preserve">Refund against 4 Aug order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refund — 5 bags unused monocouche + other returned items, against original £148.53 order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refund confirmed received 19 Aug — £72.23, slightly more than the £63.10 estimate (5 bags x £12.62), likely covered a few additional returned items beyond the monocouche. Actual figure used, not the estimate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TP invoice 1048887075</t>
   </si>
   <si>
@@ -890,6 +899,15 @@
     <t xml:space="preserve">PAID 18 Aug, part of the full £547.88 TP account settlement.</t>
   </si>
   <si>
+    <t xml:space="preserve">INV-0289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decking labour — stage 1 (25% of £17,600 quoted labour)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First stage payment — resolves the earlier open question about 4-5 stage triggers: appears to be a flat 25% per stage. 3 stages remaining (£13,200).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Scaffold erection payment — coping share (pro-rata of £2,000 cash). CAUGHT 18 Aug: paid at the time, only now logged in the Register.</t>
   </si>
   <si>
@@ -908,6 +926,21 @@
     <t xml:space="preserve">Scaffold strike complete 18 Aug, final balance paid.</t>
   </si>
   <si>
+    <t xml:space="preserve">V4FQ-17702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V4 screw top-up — 15 boxes structural subframe screws (named purpose #8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requested by Luke 20 Aug, ordered and paid 24 Aug.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decking labour — cash instalment (10% discount applies)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retires £2,222.22 of quoted value at the 10% cash discount (£2,000 paid = 90%). Not a full 25% stage — partial/interim payment. Total paid to date: £6,400 (Stage 1 £4,400 invoiced + this £2,000 cash). Quoted value remaining: £10,977.78.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skip Hire Log — pooled rubbish-removal drawdown</t>
   </si>
   <si>
@@ -1007,7 +1040,7 @@
     <t xml:space="preserve">Contingency Drawdown — £5,000 pot (agreed Lara/Luke, 1 Jul 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Named purposes: fence move/repair labour · soakaway fix before decking · drainage by the garage · additional curved-decking labour · cement &amp; bricks · coping condensation-prep (£276.42, purpose #6) · chimney cowl upgrade (£62.90, purpose #7). Luke's labour from this pot invoiced at 10% discount (extended 20 Jul) — condensation-prep material/labour and the cowl were bank transfer/direct paid, not cash, so no discount applied. Curved-decking extra labour discount status TBC. Pipe investigation (task 3.7) still flagged as a likely future purpose #8 — not yet formally added, cost unknown.</t>
+    <t xml:space="preserve">Named purposes: fence move/repair labour · ~~soakaway fix before decking~~ CANCELLED 1 Sep, cost-benefit not worth it, nothing drawn · drainage by the garage · additional curved-decking labour · cement &amp; bricks · coping condensation-prep (£276.42, purpose #6) · chimney cowl upgrade (£62.90, purpose #7) · V4 screw top-up (£141.66, purpose #8). Luke's labour from this pot invoiced at 10% discount (extended 20 Jul) — condensation-prep, the cowl, and the screw top-up were all bank transfer/direct paid, not cash, so no discount applied to any of them. Curved-decking extra labour discount status TBC. Pipe investigation (task 2.2) RESOLVED 4 Sep: no leaking pipe found — damp ground was condensation trapped under old decking, not a plumbing fault. No repair needed, purpose #9 not required. Excavation continues for decking widening (straight-line, distinct from curved-decking-labour purpose above), tracked under decking substructure, not contingency.</t>
   </si>
   <si>
     <t xml:space="preserve">Opening pot:</t>
@@ -1032,22 +1065,24 @@
   </si>
   <si>
     <t xml:space="preserve">StoveWorldUK (order #147399)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V4 Wood Flooring Ltd (V4FQ-17702)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="\£#,##0.00"/>
     <numFmt numFmtId="168" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00"/>
     <numFmt numFmtId="169" formatCode="\£#,##0.00;[RED]&quot;-£&quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1158,14 +1193,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFDC2626"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="13"/>
       <color rgb="FF0F766E"/>
       <name val="Calibri"/>
@@ -1290,7 +1317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1439,15 +1466,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1459,10 +1478,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1587,15 +1602,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1624,7 +1635,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFDC2626"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1950,17 +1961,17 @@
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">SUMIF('Invoice Register'!$B:$B,$A6,'Invoice Register'!$F:$F)</f>
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUMIFS('Invoice Register'!$F:$F,'Invoice Register'!$B:$B,$A6,'Invoice Register'!$G:$G,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F6" s="10" t="n">
         <f aca="false">C6-D6</f>
-        <v>17600</v>
-      </c>
-      <c r="G6" s="12" t="s">
+        <v>11200</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1976,15 +1987,15 @@
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">SUMIF('Invoice Register'!$B:$B,$A7,'Invoice Register'!$F:$F)</f>
-        <v>339.32</v>
+        <v>480.98</v>
       </c>
       <c r="E7" s="10" t="n">
         <f aca="false">SUMIFS('Invoice Register'!$F:$F,'Invoice Register'!$B:$B,$A7,'Invoice Register'!$G:$G,"&lt;&gt;")</f>
-        <v>339.32</v>
+        <v>480.98</v>
       </c>
       <c r="F7" s="10" t="n">
         <f aca="false">C7-D7</f>
-        <v>4660.68</v>
+        <v>4519.02</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>18</v>
@@ -2054,15 +2065,15 @@
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">SUMIF('Invoice Register'!$B:$B,$A10,'Invoice Register'!$F:$F)</f>
-        <v>1192.92</v>
+        <v>1120.69</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">SUMIFS('Invoice Register'!$F:$F,'Invoice Register'!$B:$B,$A10,'Invoice Register'!$G:$G,"&lt;&gt;")</f>
-        <v>1192.92</v>
+        <v>1120.69</v>
       </c>
       <c r="F10" s="10" t="n">
         <f aca="false">C10-D10</f>
-        <v>-62.9200000000001</v>
+        <v>9.30999999999995</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>25</v>
@@ -2105,15 +2116,15 @@
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">D5+D6+D7</f>
-        <v>32568.31</v>
+        <v>39109.97</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">E5+E6+E7</f>
-        <v>32568.31</v>
+        <v>39109.97</v>
       </c>
       <c r="F12" s="15" t="n">
         <f aca="false">F5+F6+F7</f>
-        <v>22260.68</v>
+        <v>15719.02</v>
       </c>
       <c r="G12" s="19"/>
     </row>
@@ -2128,15 +2139,15 @@
       </c>
       <c r="D13" s="22" t="n">
         <f aca="false">D8+D9+D10</f>
-        <v>11202.93</v>
+        <v>11130.7</v>
       </c>
       <c r="E13" s="22" t="n">
         <f aca="false">E8+E9+E10</f>
-        <v>11202.93</v>
+        <v>11130.7</v>
       </c>
       <c r="F13" s="22" t="n">
         <f aca="false">F8+F9+F10</f>
-        <v>-62.9300000000003</v>
+        <v>9.29999999999973</v>
       </c>
       <c r="G13" s="21"/>
     </row>
@@ -2151,15 +2162,15 @@
       </c>
       <c r="D14" s="25" t="n">
         <f aca="false">D11+D12+D13</f>
-        <v>44551.24</v>
+        <v>51020.67</v>
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">E11+E12+E13</f>
-        <v>44551.24</v>
+        <v>51020.67</v>
       </c>
       <c r="F14" s="25" t="n">
         <f aca="false">F11+F12+F13</f>
-        <v>22777.75</v>
+        <v>16308.32</v>
       </c>
       <c r="G14" s="24"/>
     </row>
@@ -2169,7 +2180,7 @@
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">'Contingency Drawdown'!$D$4</f>
-        <v>4660.68</v>
+        <v>4519.02</v>
       </c>
     </row>
   </sheetData>
@@ -2361,10 +2372,10 @@
         <v>17600</v>
       </c>
       <c r="C19" s="32" t="n">
-        <v>17600</v>
-      </c>
-      <c r="D19" s="33" t="n">
-        <v>0</v>
+        <v>6400</v>
+      </c>
+      <c r="D19" s="37" t="n">
+        <v>-11200</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>61</v>
@@ -2405,19 +2416,19 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="38" t="n">
+      <c r="B22" s="35" t="n">
         <v>1130</v>
       </c>
-      <c r="C22" s="38" t="n">
-        <v>1192.92</v>
-      </c>
-      <c r="D22" s="39" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="E22" s="37" t="s">
+      <c r="C22" s="35" t="n">
+        <v>1120.69</v>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="E22" s="34" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2425,13 +2436,13 @@
       <c r="A23" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="40" t="n">
+      <c r="B23" s="38" t="n">
         <v>1360</v>
       </c>
-      <c r="C23" s="40" t="n">
+      <c r="C23" s="38" t="n">
         <v>780</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D23" s="39" t="n">
         <v>-580</v>
       </c>
       <c r="E23" s="14" t="s">
@@ -2446,41 +2457,41 @@
         <v>5000</v>
       </c>
       <c r="C24" s="32" t="n">
-        <v>339.32</v>
-      </c>
-      <c r="D24" s="42" t="n">
-        <v>-4660.68</v>
+        <v>480.98</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>-4519.02</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="44" t="n">
+      <c r="B25" s="41" t="n">
         <v>67518.99</v>
       </c>
-      <c r="C25" s="44" t="n">
-        <v>62151.23</v>
-      </c>
-      <c r="D25" s="45" t="n">
-        <v>-5367.76</v>
-      </c>
-      <c r="E25" s="46" t="s">
+      <c r="C25" s="41" t="n">
+        <v>51020.66</v>
+      </c>
+      <c r="D25" s="42" t="n">
+        <v>-16498.33</v>
+      </c>
+      <c r="E25" s="43" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="45" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2494,95 +2505,95 @@
       <c r="E28" s="28"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="50" t="n">
+      <c r="C30" s="47" t="n">
         <v>4700</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="50" t="n">
+      <c r="C31" s="47" t="n">
         <v>5310</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="50" t="n">
+      <c r="C32" s="47" t="n">
         <v>17600</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="50" t="n">
+      <c r="C33" s="47" t="n">
         <v>32228.99</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="50" t="n">
+      <c r="C34" s="47" t="n">
         <v>1130</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="50" t="n">
+      <c r="C35" s="47" t="n">
         <v>1360</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="50" t="n">
+      <c r="C36" s="47" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51" t="s">
+      <c r="A37" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B37" s="52"/>
-      <c r="C37" s="53" t="n">
+      <c r="B37" s="49"/>
+      <c r="C37" s="50" t="n">
         <v>67328.99</v>
       </c>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="53" t="n">
+      <c r="B38" s="49"/>
+      <c r="C38" s="50" t="n">
         <f aca="false">Summary!C14</f>
         <v>67328.99</v>
       </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
+      <c r="D38" s="49"/>
+      <c r="E38" s="49"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="54" t="n">
+      <c r="B39" s="49"/>
+      <c r="C39" s="51" t="n">
         <f aca="false">67328.99-C38</f>
         <v>0</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
+      <c r="D39" s="49"/>
+      <c r="E39" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2661,7 +2672,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="55" t="n">
+      <c r="A5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -2676,16 +2687,16 @@
       <c r="E5" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F5" s="56" t="n">
+      <c r="F5" s="53" t="n">
         <v>32228.99</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="54" t="s">
         <v>95</v>
       </c>
       <c r="H5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="55" t="n">
+      <c r="A6" s="52" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -2700,10 +2711,10 @@
       <c r="E6" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="53" t="n">
         <v>2000</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="54" t="s">
         <v>95</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -2711,7 +2722,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="55" t="n">
+      <c r="A7" s="52" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -2726,10 +2737,10 @@
       <c r="E7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="56" t="n">
+      <c r="F7" s="53" t="n">
         <v>1200</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="55" t="s">
         <v>103</v>
       </c>
       <c r="H7" s="8" t="s">
@@ -2737,7 +2748,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="55" t="n">
+      <c r="A8" s="52" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -2752,10 +2763,10 @@
       <c r="E8" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="56" t="n">
+      <c r="F8" s="53" t="n">
         <v>3200</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="54" t="s">
         <v>95</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -2763,7 +2774,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="55" t="n">
+      <c r="A9" s="52" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -2778,10 +2789,10 @@
       <c r="E9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F9" s="56" t="n">
+      <c r="F9" s="53" t="n">
         <v>1710</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="54" t="s">
         <v>95</v>
       </c>
       <c r="H9" s="8" t="s">
@@ -2789,7 +2800,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="55" t="n">
+      <c r="A10" s="52" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -2804,10 +2815,10 @@
       <c r="E10" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="56" t="n">
+      <c r="F10" s="53" t="n">
         <v>1900</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="55" t="s">
         <v>113</v>
       </c>
       <c r="H10" s="8" t="s">
@@ -2815,7 +2826,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="55" t="n">
+      <c r="A11" s="52" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -2830,10 +2841,10 @@
       <c r="E11" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F11" s="56" t="n">
+      <c r="F11" s="53" t="n">
         <v>250</v>
       </c>
-      <c r="G11" s="59" t="s">
+      <c r="G11" s="56" t="s">
         <v>117</v>
       </c>
       <c r="H11" s="8" t="s">
@@ -2841,189 +2852,189 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="55" t="n">
+      <c r="A12" s="52" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>17600</v>
+      </c>
+      <c r="G12" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="56" t="n">
-        <v>17600</v>
-      </c>
-      <c r="G12" s="58" t="s">
+      <c r="H12" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="55" t="n">
+      <c r="A13" s="52" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="53" t="n">
+        <v>1130</v>
+      </c>
+      <c r="G13" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="F13" s="56" t="n">
-        <v>1130</v>
-      </c>
-      <c r="G13" s="58" t="s">
+      <c r="H13" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="55" t="n">
+      <c r="A14" s="52" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="53" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G14" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="F14" s="56" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G14" s="58" t="s">
+      <c r="H14" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="55" t="n">
+      <c r="A15" s="52" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="53" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G15" s="54" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="56" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G15" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="55" t="n">
+      <c r="A16" s="52" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="57" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G16" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="60" t="n">
-        <v>1360</v>
-      </c>
-      <c r="G16" s="58" t="s">
+      <c r="H16" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="H16" s="8" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="59" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="61"/>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="62" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="63" t="n">
+      <c r="F17" s="60" t="n">
         <f aca="false">SUM(F5:F16)</f>
         <v>67641.89</v>
       </c>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="61"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="F18" s="65" t="n">
+      <c r="A18" s="58"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="62" t="n">
         <f aca="false">Summary!$C$14</f>
         <v>67328.99</v>
       </c>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="65" t="n">
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="61" t="s">
+        <v>143</v>
+      </c>
+      <c r="F19" s="62" t="n">
         <f aca="false">F17-F18</f>
         <v>312.899999999994</v>
       </c>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="61"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3059,12 +3070,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3075,22 +3086,22 @@
         <v>4</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -3101,24 +3112,24 @@
         <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="53" t="n">
+        <v>3200</v>
+      </c>
+      <c r="G5" s="63" t="s">
         <v>154</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="56" t="n">
-        <v>3200</v>
-      </c>
-      <c r="G5" s="66" t="s">
+      <c r="H5" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="11" t="s">
         <v>156</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3126,24 +3137,24 @@
         <v>19</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="53" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G6" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="56" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G6" s="66" t="s">
+      <c r="H6" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3154,18 +3165,18 @@
         <v>24</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="53" t="n">
+        <v>480</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="56" t="n">
-        <v>480</v>
-      </c>
-      <c r="G7" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>164</v>
       </c>
       <c r="I7" s="11"/>
     </row>
@@ -3174,24 +3185,24 @@
         <v>19</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3199,24 +3210,24 @@
         <v>21</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="53" t="n">
+        <v>3610</v>
+      </c>
+      <c r="G9" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="D9" s="66"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="56" t="n">
-        <v>3610</v>
-      </c>
-      <c r="G9" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3224,24 +3235,24 @@
         <v>21</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="56" t="n">
+        <v>168</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="53" t="n">
         <v>1700</v>
       </c>
-      <c r="G10" s="66" t="s">
+      <c r="G10" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" s="11" t="s">
         <v>161</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3252,18 +3263,18 @@
         <v>24</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="56" t="n">
+        <v>169</v>
+      </c>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="53" t="n">
         <v>650</v>
       </c>
-      <c r="G11" s="66" t="s">
-        <v>160</v>
+      <c r="G11" s="63" t="s">
+        <v>159</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I11" s="11"/>
     </row>
@@ -3272,24 +3283,24 @@
         <v>21</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="56" t="n">
+        <v>164</v>
+      </c>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="66" t="s">
-        <v>160</v>
+      <c r="G12" s="63" t="s">
+        <v>159</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3297,24 +3308,24 @@
         <v>13</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="53" t="n">
+        <v>17600</v>
+      </c>
+      <c r="G13" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="56" t="n">
-        <v>17600</v>
-      </c>
-      <c r="G13" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3322,24 +3333,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3347,25 +3358,25 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="63" t="n">
+        <v>230</v>
+      </c>
+      <c r="E15" s="53" t="n">
+        <v>66.49</v>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>15292.7</v>
+      </c>
+      <c r="G15" s="63" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="66" t="n">
-        <v>230</v>
-      </c>
-      <c r="E15" s="56" t="n">
-        <v>66.49</v>
-      </c>
-      <c r="F15" s="56" t="n">
-        <v>15292.7</v>
-      </c>
-      <c r="G15" s="66" t="s">
+      <c r="H15" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I15" s="11"/>
     </row>
@@ -3374,25 +3385,25 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" s="66" t="n">
+        <v>179</v>
+      </c>
+      <c r="D16" s="63" t="n">
         <v>18</v>
       </c>
-      <c r="E16" s="56" t="n">
+      <c r="E16" s="53" t="n">
         <v>58.09</v>
       </c>
-      <c r="F16" s="56" t="n">
+      <c r="F16" s="53" t="n">
         <v>1045.62</v>
       </c>
-      <c r="G16" s="66" t="s">
+      <c r="G16" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I16" s="11"/>
     </row>
@@ -3401,28 +3412,28 @@
         <v>10</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D17" s="63" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" s="53" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="F17" s="53" t="n">
+        <v>1083.75</v>
+      </c>
+      <c r="G17" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>181</v>
-      </c>
-      <c r="D17" s="66" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" s="56" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="F17" s="56" t="n">
-        <v>1083.75</v>
-      </c>
-      <c r="G17" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3430,25 +3441,25 @@
         <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="66" t="n">
+        <v>182</v>
+      </c>
+      <c r="D18" s="63" t="n">
         <v>15</v>
       </c>
-      <c r="E18" s="56" t="n">
+      <c r="E18" s="53" t="n">
         <v>59.89</v>
       </c>
-      <c r="F18" s="56" t="n">
+      <c r="F18" s="53" t="n">
         <v>898.35</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I18" s="11"/>
     </row>
@@ -3457,25 +3468,25 @@
         <v>10</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="66" t="n">
+        <v>183</v>
+      </c>
+      <c r="D19" s="63" t="n">
         <v>24</v>
       </c>
-      <c r="E19" s="56" t="n">
+      <c r="E19" s="53" t="n">
         <v>32.08</v>
       </c>
-      <c r="F19" s="56" t="n">
+      <c r="F19" s="53" t="n">
         <v>770</v>
       </c>
-      <c r="G19" s="66" t="s">
+      <c r="G19" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I19" s="11"/>
     </row>
@@ -3484,25 +3495,25 @@
         <v>10</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="66" t="n">
+        <v>184</v>
+      </c>
+      <c r="D20" s="63" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="56" t="n">
+      <c r="E20" s="53" t="n">
         <v>10.25</v>
       </c>
-      <c r="F20" s="56" t="n">
+      <c r="F20" s="53" t="n">
         <v>61.5</v>
       </c>
-      <c r="G20" s="66" t="s">
+      <c r="G20" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I20" s="11"/>
     </row>
@@ -3511,28 +3522,28 @@
         <v>10</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D21" s="63" t="n">
+        <v>266</v>
+      </c>
+      <c r="E21" s="53" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F21" s="53" t="n">
+        <v>7554.4</v>
+      </c>
+      <c r="G21" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="D21" s="66" t="n">
-        <v>266</v>
-      </c>
-      <c r="E21" s="56" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="F21" s="56" t="n">
-        <v>7554.4</v>
-      </c>
-      <c r="G21" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3540,52 +3551,54 @@
         <v>10</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="63" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" s="53" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="F22" s="53" t="n">
+        <v>125.92</v>
+      </c>
+      <c r="G22" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="66" t="n">
-        <v>16</v>
-      </c>
-      <c r="E22" s="56" t="n">
-        <v>7.87</v>
-      </c>
-      <c r="F22" s="56" t="n">
-        <v>125.92</v>
-      </c>
-      <c r="G22" s="66" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="56" t="n">
+      <c r="E23" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="F23" s="56" t="n">
+      <c r="F23" s="53" t="n">
         <v>15</v>
       </c>
-      <c r="G23" s="66" t="s">
+      <c r="G23" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I23" s="11"/>
     </row>
@@ -3594,25 +3607,25 @@
         <v>10</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="56" t="n">
+      <c r="E24" s="53" t="n">
         <v>10.25</v>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="53" t="n">
         <v>10.25</v>
       </c>
-      <c r="G24" s="66" t="s">
+      <c r="G24" s="63" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="I24" s="11"/>
     </row>
@@ -3621,21 +3634,21 @@
         <v>10</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="56" t="n">
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="53" t="n">
         <v>5371.5</v>
       </c>
-      <c r="G25" s="66" t="s">
-        <v>151</v>
+      <c r="G25" s="63" t="s">
+        <v>150</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>192</v>
@@ -3651,12 +3664,12 @@
       <c r="C26" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="56" t="n">
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="53" t="n">
         <v>5000</v>
       </c>
-      <c r="G26" s="66" t="s">
+      <c r="G26" s="63" t="s">
         <v>17</v>
       </c>
       <c r="H26" s="8" t="s">
@@ -3676,12 +3689,12 @@
       <c r="C27" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="56" t="n">
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="53" t="n">
         <v>250</v>
       </c>
-      <c r="G27" s="66" t="s">
+      <c r="G27" s="63" t="s">
         <v>193</v>
       </c>
       <c r="H27" s="8" t="s">
@@ -3701,17 +3714,17 @@
       <c r="C28" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="66" t="n">
+      <c r="D28" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="56" t="n">
+      <c r="E28" s="53" t="n">
         <v>62.9</v>
       </c>
-      <c r="F28" s="56" t="n">
+      <c r="F28" s="53" t="n">
         <v>62.9</v>
       </c>
-      <c r="G28" s="66" t="s">
-        <v>160</v>
+      <c r="G28" s="63" t="s">
+        <v>159</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>202</v>
@@ -3721,24 +3734,24 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="52" t="s">
         <v>204</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55" t="n">
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52" t="n">
         <v>481.26</v>
       </c>
-      <c r="G29" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="H29" s="55" t="s">
+      <c r="G29" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="52" t="s">
         <v>206</v>
       </c>
       <c r="I29" s="8" t="s">
@@ -3746,20 +3759,20 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55" t="n">
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="H30" s="55" t="s">
+      <c r="G30" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" s="52" t="s">
         <v>206</v>
       </c>
       <c r="I30" s="8" t="s">
@@ -3767,28 +3780,28 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="55" t="s">
-        <v>204</v>
+      <c r="B31" s="52" t="s">
+        <v>11</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55" t="n">
-        <v>26.42</v>
-      </c>
-      <c r="G31" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" s="55" t="s">
-        <v>206</v>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="G31" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>211</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3799,30 +3812,30 @@
         <v>27</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="56" t="n">
+        <v>213</v>
+      </c>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="53" t="n">
         <v>1360</v>
       </c>
-      <c r="G32" s="66" t="s">
+      <c r="G32" s="63" t="s">
         <v>17</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>202</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C33" s="67" t="s">
-        <v>214</v>
-      </c>
-      <c r="F33" s="68" t="n">
+      <c r="C33" s="64" t="s">
+        <v>215</v>
+      </c>
+      <c r="F33" s="65" t="n">
         <f aca="false">SUM(F5:F32)</f>
-        <v>68149.57</v>
+        <v>68264.81</v>
       </c>
     </row>
   </sheetData>
@@ -3841,7 +3854,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
@@ -3855,17 +3868,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>3</v>
@@ -3874,26 +3887,26 @@
         <v>4</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="n">
+      <c r="A5" s="66" t="n">
         <v>46212</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -3903,84 +3916,84 @@
         <v>11</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F5" s="56" t="n">
+        <v>225</v>
+      </c>
+      <c r="F5" s="53" t="n">
         <v>32228.99</v>
       </c>
-      <c r="G5" s="69" t="n">
+      <c r="G5" s="66" t="n">
         <v>46212</v>
       </c>
-      <c r="H5" s="55" t="s">
-        <v>225</v>
+      <c r="H5" s="52" t="s">
+        <v>226</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="69" t="n">
+      <c r="A6" s="66" t="n">
         <v>46223</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="56" t="n">
+        <v>230</v>
+      </c>
+      <c r="F6" s="53" t="n">
         <v>311.98</v>
       </c>
-      <c r="G6" s="69" t="n">
+      <c r="G6" s="66" t="n">
         <v>46223</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>230</v>
+      <c r="H6" s="52" t="s">
+        <v>231</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="69" t="n">
+      <c r="A7" s="66" t="n">
         <v>46223</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="56" t="n">
+        <v>233</v>
+      </c>
+      <c r="F7" s="53" t="n">
         <v>111.71</v>
       </c>
-      <c r="G7" s="69" t="n">
+      <c r="G7" s="66" t="n">
         <v>46223</v>
       </c>
-      <c r="H7" s="55" t="s">
-        <v>230</v>
+      <c r="H7" s="52" t="s">
+        <v>231</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="n">
+      <c r="A8" s="66" t="n">
         <v>46223</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -3990,26 +4003,26 @@
         <v>98</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="53" t="n">
+        <v>937.5</v>
+      </c>
+      <c r="G8" s="66" t="n">
+        <v>46223</v>
+      </c>
+      <c r="H8" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="F8" s="56" t="n">
-        <v>937.5</v>
-      </c>
-      <c r="G8" s="69" t="n">
-        <v>46223</v>
-      </c>
-      <c r="H8" s="55" t="s">
-        <v>234</v>
-      </c>
       <c r="I8" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="n">
+      <c r="A9" s="66" t="n">
         <v>46227</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -4019,26 +4032,26 @@
         <v>14</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="F9" s="56" t="n">
+        <v>239</v>
+      </c>
+      <c r="F9" s="53" t="n">
         <v>3088.3</v>
       </c>
-      <c r="G9" s="69" t="n">
+      <c r="G9" s="66" t="n">
         <v>46227</v>
       </c>
-      <c r="H9" s="55" t="s">
-        <v>239</v>
+      <c r="H9" s="52" t="s">
+        <v>211</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="n">
+      <c r="A10" s="66" t="n">
         <v>46225</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -4053,28 +4066,28 @@
       <c r="E10" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="56" t="n">
+      <c r="F10" s="53" t="n">
         <v>162.96</v>
       </c>
-      <c r="G10" s="69" t="n">
+      <c r="G10" s="66" t="n">
         <v>46225</v>
       </c>
-      <c r="H10" s="55" t="s">
-        <v>230</v>
+      <c r="H10" s="52" t="s">
+        <v>231</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="69" t="n">
+      <c r="A11" s="66" t="n">
         <v>46238</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>245</v>
@@ -4082,21 +4095,21 @@
       <c r="E11" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="F11" s="56" t="n">
+      <c r="F11" s="53" t="n">
         <v>148.53</v>
       </c>
-      <c r="G11" s="69" t="n">
+      <c r="G11" s="66" t="n">
         <v>46238</v>
       </c>
-      <c r="H11" s="55" t="s">
-        <v>230</v>
+      <c r="H11" s="52" t="s">
+        <v>231</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="69" t="n">
+      <c r="A12" s="66" t="n">
         <v>46241</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -4106,26 +4119,26 @@
         <v>14</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="F12" s="56" t="n">
+      <c r="F12" s="53" t="n">
         <v>1710</v>
       </c>
-      <c r="G12" s="69" t="n">
+      <c r="G12" s="66" t="n">
         <v>46241</v>
       </c>
-      <c r="H12" s="55" t="s">
-        <v>234</v>
+      <c r="H12" s="52" t="s">
+        <v>235</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="69" t="n">
+      <c r="A13" s="66" t="n">
         <v>46244</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -4140,13 +4153,13 @@
       <c r="E13" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="F13" s="56" t="n">
+      <c r="F13" s="53" t="n">
         <v>62.9</v>
       </c>
-      <c r="G13" s="69" t="n">
+      <c r="G13" s="66" t="n">
         <v>46244</v>
       </c>
-      <c r="H13" s="55" t="s">
+      <c r="H13" s="52" t="s">
         <v>252</v>
       </c>
       <c r="I13" s="8" t="s">
@@ -4154,7 +4167,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="69" t="n">
+      <c r="A14" s="66" t="n">
         <v>46244</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -4169,13 +4182,13 @@
       <c r="E14" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F14" s="56" t="n">
+      <c r="F14" s="53" t="n">
         <v>344.16</v>
       </c>
-      <c r="G14" s="69" t="n">
+      <c r="G14" s="66" t="n">
         <v>46244</v>
       </c>
-      <c r="H14" s="55" t="s">
+      <c r="H14" s="52" t="s">
         <v>252</v>
       </c>
       <c r="I14" s="8" t="s">
@@ -4183,373 +4196,467 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="70" t="n">
+      <c r="A15" s="67" t="n">
         <v>46245</v>
       </c>
-      <c r="B15" s="71" t="s">
+      <c r="B15" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="68" t="s">
         <v>254</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="68" t="s">
         <v>258</v>
       </c>
-      <c r="E15" s="72" t="s">
+      <c r="E15" s="69" t="s">
         <v>259</v>
       </c>
-      <c r="F15" s="73" t="n">
+      <c r="F15" s="70" t="n">
         <v>-344.16</v>
       </c>
-      <c r="G15" s="70" t="n">
+      <c r="G15" s="67" t="n">
         <v>46247</v>
       </c>
-      <c r="H15" s="71" t="s">
+      <c r="H15" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="72" t="s">
+      <c r="I15" s="69" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="70" t="n">
+      <c r="A16" s="67" t="n">
         <v>46245</v>
       </c>
-      <c r="B16" s="71" t="s">
+      <c r="B16" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="71" t="s">
+      <c r="C16" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="68" t="s">
         <v>262</v>
       </c>
-      <c r="E16" s="72" t="s">
+      <c r="E16" s="69" t="s">
         <v>263</v>
       </c>
-      <c r="F16" s="73" t="n">
+      <c r="F16" s="70" t="n">
         <v>390</v>
       </c>
-      <c r="G16" s="70" t="n">
+      <c r="G16" s="67" t="n">
         <v>46246</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="I16" s="72" t="s">
+      <c r="I16" s="69" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="70" t="n">
+      <c r="A17" s="67" t="n">
         <v>46246</v>
       </c>
-      <c r="B17" s="71" t="s">
+      <c r="B17" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="68" t="s">
         <v>261</v>
       </c>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="68" t="s">
         <v>265</v>
       </c>
-      <c r="E17" s="72" t="s">
+      <c r="E17" s="69" t="s">
         <v>266</v>
       </c>
-      <c r="F17" s="73" t="n">
+      <c r="F17" s="70" t="n">
         <v>390</v>
       </c>
-      <c r="G17" s="70" t="n">
+      <c r="G17" s="67" t="n">
         <v>46246</v>
       </c>
-      <c r="H17" s="71" t="s">
+      <c r="H17" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="I17" s="72" t="s">
+      <c r="I17" s="69" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="70" t="n">
+      <c r="A18" s="67" t="n">
         <v>46247</v>
       </c>
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="68" t="s">
         <v>268</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="F18" s="73" t="n">
+      <c r="F18" s="70" t="n">
         <v>1900</v>
       </c>
-      <c r="G18" s="70" t="n">
+      <c r="G18" s="67" t="n">
         <v>46248</v>
       </c>
-      <c r="H18" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="I18" s="72" t="s">
+      <c r="H18" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="69" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="70" t="n">
+      <c r="A19" s="67" t="n">
         <v>46247</v>
       </c>
-      <c r="B19" s="71" t="s">
+      <c r="B19" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="68" t="s">
         <v>268</v>
       </c>
-      <c r="E19" s="72" t="s">
+      <c r="E19" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="F19" s="73" t="n">
+      <c r="F19" s="70" t="n">
         <v>250</v>
       </c>
-      <c r="G19" s="70" t="n">
+      <c r="G19" s="67" t="n">
         <v>46248</v>
       </c>
-      <c r="H19" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="I19" s="72" t="s">
+      <c r="H19" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I19" s="69" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="70" t="n">
+      <c r="A20" s="67" t="n">
         <v>46250</v>
       </c>
-      <c r="B20" s="71" t="s">
+      <c r="B20" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="68" t="s">
         <v>273</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="68" t="s">
         <v>274</v>
       </c>
-      <c r="E20" s="72" t="s">
+      <c r="E20" s="69" t="s">
         <v>275</v>
       </c>
-      <c r="F20" s="73" t="n">
+      <c r="F20" s="70" t="n">
         <v>47.99</v>
       </c>
-      <c r="G20" s="70" t="n">
+      <c r="G20" s="67" t="n">
         <v>46250</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="68" t="s">
         <v>276</v>
       </c>
-      <c r="I20" s="72" t="s">
+      <c r="I20" s="69" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="70" t="n">
+      <c r="A21" s="67" t="n">
         <v>46251</v>
       </c>
-      <c r="B21" s="71" t="s">
+      <c r="B21" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="D21" s="71" t="s">
+      <c r="D21" s="68" t="s">
         <v>278</v>
       </c>
-      <c r="E21" s="72" t="s">
+      <c r="E21" s="69" t="s">
         <v>279</v>
       </c>
-      <c r="F21" s="73" t="n">
+      <c r="F21" s="70" t="n">
         <v>481.28</v>
       </c>
-      <c r="G21" s="70" t="n">
+      <c r="G21" s="67" t="n">
         <v>46252</v>
       </c>
-      <c r="H21" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="I21" s="72" t="s">
+      <c r="H21" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I21" s="69" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="70"/>
-      <c r="B22" s="71"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="72"/>
+      <c r="A22" s="67" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B22" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="69" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="70" t="n">
+        <v>-72.23</v>
+      </c>
+      <c r="G22" s="67" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="69" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="70" t="n">
+      <c r="A23" s="67" t="n">
         <v>46251</v>
       </c>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="D23" s="71" t="s">
-        <v>281</v>
-      </c>
-      <c r="E23" s="72" t="s">
-        <v>282</v>
-      </c>
-      <c r="F23" s="73" t="n">
+      <c r="D23" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="69" t="s">
+        <v>285</v>
+      </c>
+      <c r="F23" s="70" t="n">
         <v>26.42</v>
       </c>
-      <c r="G23" s="70" t="n">
+      <c r="G23" s="67" t="n">
         <v>46252</v>
       </c>
-      <c r="H23" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="I23" s="72" t="s">
-        <v>283</v>
+      <c r="H23" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I23" s="69" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="70" t="n">
+      <c r="A24" s="67" t="n">
         <v>46244</v>
       </c>
-      <c r="B24" s="71" t="s">
+      <c r="B24" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="68" t="s">
         <v>204</v>
       </c>
-      <c r="D24" s="71" t="s">
-        <v>284</v>
-      </c>
-      <c r="E24" s="72" t="s">
-        <v>285</v>
-      </c>
-      <c r="F24" s="73" t="n">
+      <c r="D24" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="E24" s="69" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" s="70" t="n">
         <v>40.18</v>
       </c>
-      <c r="G24" s="70" t="n">
+      <c r="G24" s="67" t="n">
         <v>46252</v>
       </c>
-      <c r="H24" s="71" t="s">
-        <v>239</v>
-      </c>
-      <c r="I24" s="72" t="s">
-        <v>286</v>
+      <c r="H24" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I24" s="69" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="70"/>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="72"/>
+      <c r="A25" s="67" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B25" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="E25" s="69" t="s">
+        <v>291</v>
+      </c>
+      <c r="F25" s="70" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G25" s="67" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="I25" s="69" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="74" t="n">
+      <c r="A26" s="66" t="n">
         <v>46223</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="55" t="s">
-        <v>234</v>
+      <c r="D26" s="52" t="s">
+        <v>235</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="F26" s="55" t="n">
+        <v>293</v>
+      </c>
+      <c r="F26" s="52" t="n">
         <v>1062.5</v>
       </c>
-      <c r="G26" s="74" t="n">
+      <c r="G26" s="66" t="n">
         <v>46223</v>
       </c>
-      <c r="H26" s="55" t="s">
-        <v>234</v>
+      <c r="H26" s="52" t="s">
+        <v>235</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="74" t="n">
+      <c r="A27" s="66" t="n">
         <v>46252</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="52" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F27" s="55" t="n">
+        <v>295</v>
+      </c>
+      <c r="F27" s="52" t="n">
         <v>562.5</v>
       </c>
-      <c r="G27" s="74" t="n">
+      <c r="G27" s="66" t="n">
         <v>46252</v>
       </c>
-      <c r="H27" s="55" t="s">
+      <c r="H27" s="52" t="s">
         <v>193</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="74" t="n">
+      <c r="A28" s="66" t="n">
         <v>46252</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="52" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F28" s="55" t="n">
+        <v>297</v>
+      </c>
+      <c r="F28" s="52" t="n">
         <v>637.5</v>
       </c>
-      <c r="G28" s="74" t="n">
+      <c r="G28" s="66" t="n">
         <v>46252</v>
       </c>
-      <c r="H28" s="55" t="s">
+      <c r="H28" s="52" t="s">
         <v>193</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>292</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="66" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F29" s="52" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="G29" s="66" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H29" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="66" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F30" s="52" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G30" s="66" t="n">
+        <v>46269</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4581,63 +4688,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B4" s="75" t="n">
+        <v>306</v>
+      </c>
+      <c r="B4" s="71" t="n">
         <v>1360</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="76" t="n">
+        <v>307</v>
+      </c>
+      <c r="D4" s="72" t="n">
         <f aca="false">B4-SUM(E8:E40)</f>
         <v>580</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="n">
+      <c r="A8" s="66" t="n">
         <v>46244</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>254</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E8" s="56" t="n">
+        <v>315</v>
+      </c>
+      <c r="E8" s="53" t="n">
         <v>344.16</v>
       </c>
       <c r="F8" s="10" t="n">
@@ -4646,19 +4753,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="n">
+      <c r="A9" s="67" t="n">
         <v>46245</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="69" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>306</v>
-      </c>
-      <c r="E9" s="73" t="n">
+      <c r="C9" s="69" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>317</v>
+      </c>
+      <c r="E9" s="70" t="n">
         <v>-344.16</v>
       </c>
       <c r="F9" s="10" t="n">
@@ -4667,19 +4774,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="n">
+      <c r="A10" s="67" t="n">
         <v>46245</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="C10" s="72" t="s">
-        <v>307</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="E10" s="73" t="n">
+      <c r="C10" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="70" t="n">
         <v>390</v>
       </c>
       <c r="F10" s="10" t="n">
@@ -4688,19 +4795,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="70" t="n">
+      <c r="A11" s="67" t="n">
         <v>46246</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="C11" s="72" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="E11" s="73" t="n">
+      <c r="C11" s="69" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="70" t="n">
         <v>390</v>
       </c>
       <c r="F11" s="10" t="n">
@@ -4709,154 +4816,154 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="77"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="79"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="75"/>
       <c r="F12" s="10" t="str">
         <f aca="false">IF(E12="","",$B$4-SUM($E$8:E12))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="79"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="75"/>
       <c r="F13" s="10" t="str">
         <f aca="false">IF(E13="","",$B$4-SUM($E$8:E13))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="79"/>
+      <c r="A14" s="73"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="75"/>
       <c r="F14" s="10" t="str">
         <f aca="false">IF(E14="","",$B$4-SUM($E$8:E14))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="10" t="str">
         <f aca="false">IF(E15="","",$B$4-SUM($E$8:E15))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="79"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="75"/>
       <c r="F16" s="10" t="str">
         <f aca="false">IF(E16="","",$B$4-SUM($E$8:E16))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="75"/>
       <c r="F17" s="10" t="str">
         <f aca="false">IF(E17="","",$B$4-SUM($E$8:E17))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="79"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
       <c r="F18" s="10" t="str">
         <f aca="false">IF(E18="","",$B$4-SUM($E$8:E18))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="79"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="75"/>
       <c r="F19" s="10" t="str">
         <f aca="false">IF(E19="","",$B$4-SUM($E$8:E19))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="77"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="79"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
       <c r="F20" s="10" t="str">
         <f aca="false">IF(E20="","",$B$4-SUM($E$8:E20))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="77"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="79"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="10" t="str">
         <f aca="false">IF(E21="","",$B$4-SUM($E$8:E21))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="77"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="79"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75"/>
       <c r="F22" s="10" t="str">
         <f aca="false">IF(E22="","",$B$4-SUM($E$8:E22))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="79"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="75"/>
       <c r="F23" s="10" t="str">
         <f aca="false">IF(E23="","",$B$4-SUM($E$8:E23))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="79"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="75"/>
       <c r="F24" s="10" t="str">
         <f aca="false">IF(E24="","",$B$4-SUM($E$8:E24))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="79"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="75"/>
       <c r="F25" s="10" t="str">
         <f aca="false">IF(E25="","",$B$4-SUM($E$8:E25))</f>
         <v/>
@@ -4891,63 +4998,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="B4" s="75" t="n">
+        <v>306</v>
+      </c>
+      <c r="B4" s="71" t="n">
         <v>1130</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="76" t="n">
+        <v>307</v>
+      </c>
+      <c r="D4" s="72" t="n">
         <f aca="false">B4-SUM(E8:E40)</f>
         <v>-62.9000000000001</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>301</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="69" t="n">
+      <c r="A8" s="66" t="n">
         <v>46223</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>314</v>
-      </c>
-      <c r="E8" s="56" t="n">
+        <v>324</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="53" t="n">
         <v>311.98</v>
       </c>
       <c r="F8" s="10" t="n">
@@ -4956,19 +5063,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="69" t="n">
+      <c r="A9" s="66" t="n">
         <v>46225</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>241</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="56" t="n">
+        <v>326</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="53" t="n">
         <v>162.96</v>
       </c>
       <c r="F9" s="10" t="n">
@@ -4977,19 +5084,19 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="69" t="n">
+      <c r="A10" s="66" t="n">
         <v>46238</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="56" t="n">
+        <v>328</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="E10" s="53" t="n">
         <v>148.53</v>
       </c>
       <c r="F10" s="10" t="n">
@@ -4998,19 +5105,19 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="70" t="n">
+      <c r="A11" s="67" t="n">
         <v>46250</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="68" t="s">
         <v>273</v>
       </c>
-      <c r="C11" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>320</v>
-      </c>
-      <c r="E11" s="73" t="n">
+      <c r="C11" s="69" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>331</v>
+      </c>
+      <c r="E11" s="70" t="n">
         <v>47.99</v>
       </c>
       <c r="F11" s="10" t="n">
@@ -5019,19 +5126,19 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="70" t="n">
+      <c r="A12" s="67" t="n">
         <v>46251</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="71" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="73" t="n">
+      <c r="C12" s="69" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="70" t="n">
         <v>481.26</v>
       </c>
       <c r="F12" s="10" t="n">
@@ -5040,30 +5147,30 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="70"/>
-      <c r="B13" s="71"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="73"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="10" t="str">
         <f aca="false">IF(E13="","",$B$4-SUM($E$8:E13))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70" t="n">
+      <c r="A14" s="67" t="n">
         <v>46244</v>
       </c>
-      <c r="B14" s="72" t="s">
-        <v>323</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>324</v>
-      </c>
-      <c r="D14" s="71" t="s">
-        <v>322</v>
-      </c>
-      <c r="E14" s="73" t="n">
+      <c r="B14" s="69" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E14" s="70" t="n">
         <v>40.18</v>
       </c>
       <c r="F14" s="10" t="n">
@@ -5072,121 +5179,121 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="70"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="73"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="10" t="str">
         <f aca="false">IF(E15="","",$B$4-SUM($E$8:E15))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="79"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="75"/>
       <c r="F16" s="10" t="str">
         <f aca="false">IF(E16="","",$B$4-SUM($E$8:E16))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="75"/>
       <c r="F17" s="10" t="str">
         <f aca="false">IF(E17="","",$B$4-SUM($E$8:E17))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="79"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
       <c r="F18" s="10" t="str">
         <f aca="false">IF(E18="","",$B$4-SUM($E$8:E18))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="79"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="75"/>
       <c r="F19" s="10" t="str">
         <f aca="false">IF(E19="","",$B$4-SUM($E$8:E19))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="77"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="79"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
       <c r="F20" s="10" t="str">
         <f aca="false">IF(E20="","",$B$4-SUM($E$8:E20))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="77"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="79"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="10" t="str">
         <f aca="false">IF(E21="","",$B$4-SUM($E$8:E21))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="77"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="79"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75"/>
       <c r="F22" s="10" t="str">
         <f aca="false">IF(E22="","",$B$4-SUM($E$8:E22))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="79"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="75"/>
       <c r="F23" s="10" t="str">
         <f aca="false">IF(E23="","",$B$4-SUM($E$8:E23))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="79"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="75"/>
       <c r="F24" s="10" t="str">
         <f aca="false">IF(E24="","",$B$4-SUM($E$8:E24))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="79"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="75"/>
       <c r="F25" s="10" t="str">
         <f aca="false">IF(E25="","",$B$4-SUM($E$8:E25))</f>
         <v/>
@@ -5219,57 +5326,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B4" s="75" t="n">
+        <v>338</v>
+      </c>
+      <c r="B4" s="71" t="n">
         <v>5000</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D4" s="76" t="n">
+        <v>307</v>
+      </c>
+      <c r="D4" s="72" t="n">
         <f aca="false">B4-SUM(D8:D40)</f>
-        <v>4660.68</v>
+        <v>4519.02</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="70" t="n">
+      <c r="A8" s="67" t="n">
         <v>46248</v>
       </c>
-      <c r="B8" s="72" t="s">
-        <v>330</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>331</v>
-      </c>
-      <c r="D8" s="73" t="n">
+      <c r="B8" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="D8" s="70" t="n">
         <v>250</v>
       </c>
       <c r="E8" s="10" t="n">
@@ -5278,16 +5385,16 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="70" t="n">
+      <c r="A9" s="67" t="n">
         <v>46251</v>
       </c>
-      <c r="B9" s="72" t="s">
-        <v>332</v>
-      </c>
-      <c r="C9" s="72" t="s">
+      <c r="B9" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="73" t="n">
+      <c r="D9" s="70" t="n">
         <v>26.42</v>
       </c>
       <c r="E9" s="10" t="n">
@@ -5296,16 +5403,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="70" t="n">
+      <c r="A10" s="67" t="n">
         <v>46251</v>
       </c>
-      <c r="B10" s="72" t="s">
-        <v>333</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>334</v>
-      </c>
-      <c r="D10" s="73" t="n">
+      <c r="B10" s="69" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" s="70" t="n">
         <v>62.9</v>
       </c>
       <c r="E10" s="10" t="n">
@@ -5314,150 +5421,158 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="77"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="10" t="str">
+      <c r="A11" s="67" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="70" t="n">
+        <v>141.66</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <f aca="false">IF(D11="","",$B$4-SUM($D$8:D11))</f>
-        <v/>
+        <v>4519.02</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="77"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="79"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="10" t="str">
         <f aca="false">IF(D12="","",$B$4-SUM($D$8:D12))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="10" t="str">
         <f aca="false">IF(D13="","",$B$4-SUM($D$8:D13))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="77"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
+      <c r="A14" s="73"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="10" t="str">
         <f aca="false">IF(D14="","",$B$4-SUM($D$8:D14))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="77"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="79"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="10" t="str">
         <f aca="false">IF(D15="","",$B$4-SUM($D$8:D15))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="77"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="79"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="75"/>
       <c r="E16" s="10" t="str">
         <f aca="false">IF(D16="","",$B$4-SUM($D$8:D16))</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="77"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="79"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="75"/>
       <c r="E17" s="10" t="str">
         <f aca="false">IF(D17="","",$B$4-SUM($D$8:D17))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="77"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="79"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="74"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="75"/>
       <c r="E18" s="10" t="str">
         <f aca="false">IF(D18="","",$B$4-SUM($D$8:D18))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="77"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="79"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="10" t="str">
         <f aca="false">IF(D19="","",$B$4-SUM($D$8:D19))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="77"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="75"/>
       <c r="E20" s="10" t="str">
         <f aca="false">IF(D20="","",$B$4-SUM($D$8:D20))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="77"/>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="79"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="74"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="10" t="str">
         <f aca="false">IF(D21="","",$B$4-SUM($D$8:D21))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="77"/>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="79"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="75"/>
       <c r="E22" s="10" t="str">
         <f aca="false">IF(D22="","",$B$4-SUM($D$8:D22))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="77"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="74"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="10" t="str">
         <f aca="false">IF(D23="","",$B$4-SUM($D$8:D23))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="77"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="79"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="75"/>
       <c r="E24" s="10" t="str">
         <f aca="false">IF(D24="","",$B$4-SUM($D$8:D24))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="77"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="75"/>
       <c r="E25" s="10" t="str">
         <f aca="false">IF(D25="","",$B$4-SUM($D$8:D25))</f>
         <v/>
